--- a/Tests Data/Kyocera KB260-6BPA/Single-diode model/G = 735 W.m^-2 and T = 33.6 ºC/Single-diode emulator - Kyocera KB260-6BPA (ref = STC, G = 735 and T = 33,6).xlsx
+++ b/Tests Data/Kyocera KB260-6BPA/Single-diode model/G = 735 W.m^-2 and T = 33.6 ºC/Single-diode emulator - Kyocera KB260-6BPA (ref = STC, G = 735 and T = 33,6).xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Gabriel\Desktop\Stage_GeePs\Test Data - new\Kyocera KB260-6BPA\Single-diode model\G = 735 W.m^-2 and T = 33.6 ºC\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Gabriel\Desktop\Stage_GeePs\PV-emulator\Tests Data\Kyocera KB260-6BPA\Single-diode model\G = 735 W.m^-2 and T = 33.6 ºC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD2FD8E1-4BE1-4272-A136-BCC79BBFE1F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{251658E7-63E4-4FFF-B904-1E5C87C5BDED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{217CCB4B-160F-4504-987F-9C10DFEEC66E}"/>
+    <workbookView xWindow="32850" yWindow="0" windowWidth="16545" windowHeight="15585" xr2:uid="{217CCB4B-160F-4504-987F-9C10DFEEC66E}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -476,7 +476,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5B8D570-ED79-418B-A1D1-0F000D275672}">
-  <dimension ref="A1:P19"/>
+  <dimension ref="A1:P18"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="5" max="5" width="8.5703125" customWidth="1"/>
@@ -537,57 +537,57 @@
         <v>60</v>
       </c>
       <c r="B2">
-        <v>2.9</v>
+        <v>2.77</v>
       </c>
       <c r="C2">
         <f>A2*B2</f>
-        <v>174</v>
+        <v>166.2</v>
       </c>
       <c r="D2">
-        <v>24.15</v>
+        <v>22.98</v>
       </c>
       <c r="E2">
-        <v>6.7</v>
+        <v>6.75</v>
       </c>
       <c r="F2">
         <f>D2*E2</f>
-        <v>161.80500000000001</v>
+        <v>155.11500000000001</v>
       </c>
       <c r="G2">
         <f>D2/E2</f>
-        <v>3.6044776119402981</v>
+        <v>3.4044444444444446</v>
       </c>
       <c r="H2">
-        <v>38.970112</v>
+        <v>38.970061999999999</v>
       </c>
       <c r="I2">
-        <v>10.432715999999999</v>
+        <v>11.051579</v>
       </c>
       <c r="J2">
-        <v>24.568944999999999</v>
+        <v>23.384464000000001</v>
       </c>
       <c r="K2">
-        <v>6.5773700000000002</v>
+        <v>6.6316360000000003</v>
       </c>
       <c r="L2">
         <f>J2/K2</f>
-        <v>3.7353752335659998</v>
+        <v>3.5261983619125057</v>
       </c>
       <c r="M2">
         <f>ABS(J2-D2)/D2*100</f>
-        <v>1.7347619047619081</v>
+        <v>1.7600696257615351</v>
       </c>
       <c r="N2">
         <f>ABS(K2-E2)/E2*100</f>
-        <v>1.8302985074626867</v>
+        <v>1.753540740740736</v>
       </c>
       <c r="O2">
         <f t="shared" ref="O2:O19" si="0">(ABS(L2-G2)/G2)*100</f>
-        <v>3.6315282190153253</v>
+        <v>3.5763226410331259</v>
       </c>
       <c r="P2">
         <f t="shared" ref="P2:P19" si="1">(F2/C2)*100</f>
-        <v>92.99137931034484</v>
+        <v>93.330324909747304</v>
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
@@ -595,57 +595,57 @@
         <v>60</v>
       </c>
       <c r="B3">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="C3">
         <f>A3*B3</f>
-        <v>180</v>
+        <v>172.79999999999998</v>
       </c>
       <c r="D3">
-        <v>25.17</v>
+        <v>24.22</v>
       </c>
       <c r="E3">
-        <v>6.68</v>
+        <v>6.65</v>
       </c>
       <c r="F3">
         <f>D3*E3</f>
-        <v>168.13560000000001</v>
+        <v>161.06299999999999</v>
       </c>
       <c r="G3">
         <f>D3/E3</f>
-        <v>3.7679640718562877</v>
+        <v>3.6421052631578945</v>
       </c>
       <c r="H3">
-        <v>38.478245000000001</v>
+        <v>38.970139000000003</v>
       </c>
       <c r="I3">
-        <v>9.8528520000000004</v>
+        <v>10.476988</v>
       </c>
       <c r="J3">
-        <v>25.582467999999999</v>
+        <v>24.569762999999998</v>
       </c>
       <c r="K3">
-        <v>6.5507220000000004</v>
+        <v>6.6054959999999996</v>
       </c>
       <c r="L3">
         <f>J3/K3</f>
-        <v>3.9052898291211253</v>
+        <v>3.7195939563054763</v>
       </c>
       <c r="M3">
         <f>ABS(J3-D3)/D3*100</f>
-        <v>1.6387286452125425</v>
+        <v>1.4441081750619298</v>
       </c>
       <c r="N3">
         <f>ABS(K3-E3)/E3*100</f>
-        <v>1.935299401197595</v>
+        <v>0.66923308270677839</v>
       </c>
       <c r="O3">
         <f t="shared" ref="O3" si="2">(ABS(L3-G3)/G3)*100</f>
-        <v>3.6445612178351823</v>
+        <v>2.1275797251503668</v>
       </c>
       <c r="P3">
         <f t="shared" ref="P3" si="3">(F3/C3)*100</f>
-        <v>93.408666666666676</v>
+        <v>93.207754629629633</v>
       </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.25">
@@ -653,57 +653,57 @@
         <v>60</v>
       </c>
       <c r="B4">
-        <v>3.09</v>
+        <v>3</v>
       </c>
       <c r="C4">
         <f t="shared" ref="C4:C16" si="4">A2*B4</f>
-        <v>185.39999999999998</v>
+        <v>180</v>
       </c>
       <c r="D4">
-        <v>26.24</v>
+        <v>25.23</v>
       </c>
       <c r="E4">
-        <v>6.64</v>
+        <v>6.71</v>
       </c>
       <c r="F4">
         <f>D4*E4</f>
-        <v>174.23359999999997</v>
+        <v>169.29329999999999</v>
       </c>
       <c r="G4">
         <f>D4/E4</f>
-        <v>3.9518072289156625</v>
+        <v>3.7600596125186292</v>
       </c>
       <c r="H4">
-        <v>38.480353999999998</v>
+        <v>38.970100000000002</v>
       </c>
       <c r="I4">
-        <v>9.3959589999999995</v>
+        <v>10.006746</v>
       </c>
       <c r="J4">
-        <v>26.636724000000001</v>
+        <v>25.593412000000001</v>
       </c>
       <c r="K4">
-        <v>6.504035</v>
+        <v>6.571879</v>
       </c>
       <c r="L4">
         <f>J4/K4</f>
-        <v>4.0954152306990972</v>
+        <v>3.8943827176367671</v>
       </c>
       <c r="M4">
         <f t="shared" ref="M4:M19" si="5">ABS(J4-D4)/D4*100</f>
-        <v>1.5119054878048879</v>
+        <v>1.4403963535473654</v>
       </c>
       <c r="N4">
         <f t="shared" ref="N4:N19" si="6">ABS(K4-E4)/E4*100</f>
-        <v>2.0476656626505974</v>
+        <v>2.0584351713859901</v>
       </c>
       <c r="O4">
         <f t="shared" si="0"/>
-        <v>3.6339829719588659</v>
+        <v>3.5723663707598314</v>
       </c>
       <c r="P4">
         <f t="shared" si="1"/>
-        <v>93.977130528586841</v>
+        <v>94.05183333333332</v>
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
@@ -711,57 +711,57 @@
         <v>60</v>
       </c>
       <c r="B5">
-        <v>3.14</v>
+        <v>3.1</v>
       </c>
       <c r="C5">
         <f t="shared" si="4"/>
-        <v>188.4</v>
+        <v>186</v>
       </c>
       <c r="D5">
-        <v>27.37</v>
+        <v>26.31</v>
       </c>
       <c r="E5" s="3">
-        <v>6.53</v>
+        <v>6.68</v>
       </c>
       <c r="F5">
         <f>D5*E5</f>
-        <v>178.7261</v>
+        <v>175.7508</v>
       </c>
       <c r="G5">
         <f>D5/E5</f>
-        <v>4.1914241960183771</v>
+        <v>3.9386227544910177</v>
       </c>
       <c r="H5">
-        <v>38.482475000000001</v>
+        <v>38.478721999999998</v>
       </c>
       <c r="I5">
-        <v>8.9081689999999991</v>
+        <v>9.3974969999999995</v>
       </c>
       <c r="J5">
-        <v>27.760311000000002</v>
+        <v>26.668896</v>
       </c>
       <c r="K5">
-        <v>6.4261340000000002</v>
+        <v>6.5132329999999996</v>
       </c>
       <c r="L5">
         <f t="shared" ref="L5:L15" si="7">J5/K5</f>
-        <v>4.3199085173138316</v>
+        <v>4.0945711599753922</v>
       </c>
       <c r="M5">
         <f t="shared" si="5"/>
-        <v>1.4260540738034364</v>
+        <v>1.3641049030786829</v>
       </c>
       <c r="N5">
         <f t="shared" si="6"/>
-        <v>1.5905972434915774</v>
+        <v>2.496511976047906</v>
       </c>
       <c r="O5">
         <f t="shared" si="0"/>
-        <v>3.0654096385068241</v>
+        <v>3.9594654072049478</v>
       </c>
       <c r="P5">
         <f t="shared" si="1"/>
-        <v>94.865233545647556</v>
+        <v>94.489677419354834</v>
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.25">
@@ -769,57 +769,57 @@
         <v>60</v>
       </c>
       <c r="B6">
-        <v>3.21</v>
+        <v>3.16</v>
       </c>
       <c r="C6">
         <f t="shared" si="4"/>
-        <v>192.6</v>
+        <v>189.60000000000002</v>
       </c>
       <c r="D6">
-        <v>28.15</v>
+        <v>27.33</v>
       </c>
       <c r="E6" s="3">
-        <v>6.45</v>
+        <v>6.59</v>
       </c>
       <c r="F6">
         <f>D6*E6</f>
-        <v>181.5675</v>
+        <v>180.10469999999998</v>
       </c>
       <c r="G6">
         <f>D6/E6</f>
-        <v>4.3643410852713176</v>
+        <v>4.1471927162367219</v>
       </c>
       <c r="H6">
-        <v>38.480614000000003</v>
+        <v>38.481833999999999</v>
       </c>
       <c r="I6">
-        <v>8.5700520000000004</v>
+        <v>8.9497090000000004</v>
       </c>
       <c r="J6">
-        <v>28.505875</v>
+        <v>27.661718</v>
       </c>
       <c r="K6">
-        <v>6.3485690000000004</v>
+        <v>6.4332779999999996</v>
       </c>
       <c r="L6">
         <f t="shared" ref="L6" si="8">J6/K6</f>
-        <v>4.4901260425774687</v>
+        <v>4.2997858945315288</v>
       </c>
       <c r="M6">
         <f t="shared" si="5"/>
-        <v>1.2642095914742488</v>
+        <v>1.2137504573728584</v>
       </c>
       <c r="N6">
         <f t="shared" si="6"/>
-        <v>1.5725736434108499</v>
+        <v>2.3781790591805807</v>
       </c>
       <c r="O6">
         <f t="shared" si="0"/>
-        <v>2.8821064817928059</v>
+        <v>3.6794330221835989</v>
       </c>
       <c r="P6">
         <f t="shared" si="1"/>
-        <v>94.271806853582547</v>
+        <v>94.991930379746819</v>
       </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.25">
@@ -827,57 +827,57 @@
         <v>60</v>
       </c>
       <c r="B7">
-        <v>3.26</v>
+        <v>3.17</v>
       </c>
       <c r="C7">
         <f t="shared" si="4"/>
-        <v>195.6</v>
+        <v>190.2</v>
       </c>
       <c r="D7">
-        <v>29.03</v>
+        <v>28.23</v>
       </c>
       <c r="E7">
-        <v>6.38</v>
+        <v>6.42</v>
       </c>
       <c r="F7">
         <f t="shared" ref="F7" si="9">D7*E7</f>
-        <v>185.2114</v>
+        <v>181.23660000000001</v>
       </c>
       <c r="G7">
         <f t="shared" ref="G7" si="10">D7/E7</f>
-        <v>4.5501567398119125</v>
+        <v>4.3971962616822431</v>
       </c>
       <c r="H7">
-        <v>38.481715999999999</v>
+        <v>38.481712000000002</v>
       </c>
       <c r="I7">
-        <v>8.1495789999999992</v>
+        <v>8.5261759999999995</v>
       </c>
       <c r="J7">
-        <v>29.370398999999999</v>
+        <v>28.555620000000001</v>
       </c>
       <c r="K7">
-        <v>6.2200030000000002</v>
+        <v>6.3269080000000004</v>
       </c>
       <c r="L7">
         <f t="shared" si="7"/>
-        <v>4.7219268222217901</v>
+        <v>4.5133610287995332</v>
       </c>
       <c r="M7">
         <f t="shared" si="5"/>
-        <v>1.1725766448501478</v>
+        <v>1.1534537725823615</v>
       </c>
       <c r="N7">
         <f t="shared" si="6"/>
-        <v>2.5077899686520335</v>
+        <v>1.4500311526479674</v>
       </c>
       <c r="O7">
         <f t="shared" si="0"/>
-        <v>3.7750366027386115</v>
+        <v>2.6417917282784349</v>
       </c>
       <c r="P7">
         <f t="shared" si="1"/>
-        <v>94.688854805725981</v>
+        <v>95.287381703470047</v>
       </c>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.25">
@@ -885,57 +885,57 @@
         <v>60</v>
       </c>
       <c r="B8">
-        <v>3.23</v>
+        <v>3.25</v>
       </c>
       <c r="C8">
         <f t="shared" si="4"/>
-        <v>193.8</v>
+        <v>195</v>
       </c>
       <c r="D8">
-        <v>29.57</v>
+        <v>29.18</v>
       </c>
       <c r="E8">
-        <v>6.22</v>
+        <v>6.38</v>
       </c>
       <c r="F8">
         <f>D8*E8</f>
-        <v>183.9254</v>
+        <v>186.16839999999999</v>
       </c>
       <c r="G8">
         <f t="shared" ref="G8:G12" si="11">D8/E8</f>
-        <v>4.754019292604502</v>
+        <v>4.5736677115987465</v>
       </c>
       <c r="H8">
-        <v>38.484969999999997</v>
+        <v>38.97081</v>
       </c>
       <c r="I8">
-        <v>7.8853330000000001</v>
+        <v>8.1682190000000006</v>
       </c>
       <c r="J8">
-        <v>29.870871000000001</v>
+        <v>29.45533</v>
       </c>
       <c r="K8">
-        <v>6.1203570000000003</v>
+        <v>6.1737900000000003</v>
       </c>
       <c r="L8">
         <f t="shared" si="7"/>
-        <v>4.8805765742096421</v>
+        <v>4.7710288169827608</v>
       </c>
       <c r="M8">
         <f t="shared" si="5"/>
-        <v>1.0174873182279363</v>
+        <v>0.94355723098012434</v>
       </c>
       <c r="N8">
         <f t="shared" si="6"/>
-        <v>1.6019774919614065</v>
+        <v>3.2321316614419997</v>
       </c>
       <c r="O8">
         <f t="shared" si="0"/>
-        <v>2.6621112329522205</v>
+        <v>4.3151605632282761</v>
       </c>
       <c r="P8">
         <f t="shared" si="1"/>
-        <v>94.904747162022701</v>
+        <v>95.47097435897436</v>
       </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.25">
@@ -943,57 +943,57 @@
         <v>60</v>
       </c>
       <c r="B9">
-        <v>3.24</v>
+        <v>3.22</v>
       </c>
       <c r="C9">
         <f t="shared" ref="C9" si="12">A7*B9</f>
-        <v>194.4</v>
+        <v>193.20000000000002</v>
       </c>
       <c r="D9">
-        <v>30.11</v>
+        <v>30.16</v>
       </c>
       <c r="E9">
-        <v>6.13</v>
+        <v>6.15</v>
       </c>
       <c r="F9">
         <f>D9*E9</f>
-        <v>184.57429999999999</v>
+        <v>185.48400000000001</v>
       </c>
       <c r="G9">
         <f t="shared" ref="G9" si="13">D9/E9</f>
-        <v>4.9119086460032628</v>
+        <v>4.9040650406504058</v>
       </c>
       <c r="H9">
-        <v>38.479599</v>
+        <v>38.484023999999998</v>
       </c>
       <c r="I9">
-        <v>7.5884410000000004</v>
+        <v>7.5276269999999998</v>
       </c>
       <c r="J9">
-        <v>30.389585</v>
+        <v>30.391579</v>
       </c>
       <c r="K9">
-        <v>5.9930339999999998</v>
+        <v>5.9447130000000001</v>
       </c>
       <c r="L9">
         <f t="shared" ref="L9" si="14">J9/K9</f>
-        <v>5.0708180530929745</v>
+        <v>5.1123711102621776</v>
       </c>
       <c r="M9">
         <f t="shared" ref="M9" si="15">ABS(J9-D9)/D9*100</f>
-        <v>0.928545333776157</v>
+        <v>0.76783488063660466</v>
       </c>
       <c r="N9">
         <f t="shared" ref="N9" si="16">ABS(K9-E9)/E9*100</f>
-        <v>2.2343556280587302</v>
+        <v>3.3380000000000036</v>
       </c>
       <c r="O9">
         <f t="shared" ref="O9" si="17">(ABS(L9-G9)/G9)*100</f>
-        <v>3.2351865342408921</v>
+        <v>4.2476204513010503</v>
       </c>
       <c r="P9">
         <f t="shared" ref="P9" si="18">(F9/C9)*100</f>
-        <v>94.945627572016463</v>
+        <v>96.006211180124225</v>
       </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.25">
@@ -1001,57 +1001,57 @@
         <v>60</v>
       </c>
       <c r="B10">
-        <v>3.2</v>
+        <v>3.11</v>
       </c>
       <c r="C10">
-        <f t="shared" si="4"/>
-        <v>192</v>
+        <f t="shared" ref="C10" si="19">A8*B10</f>
+        <v>186.6</v>
       </c>
       <c r="D10">
-        <v>30.66</v>
+        <v>31.23</v>
       </c>
       <c r="E10">
-        <v>5.94</v>
+        <v>5.7</v>
       </c>
       <c r="F10">
         <f>D10*E10</f>
-        <v>182.12040000000002</v>
+        <v>178.011</v>
       </c>
       <c r="G10">
-        <f>D10/E10</f>
-        <v>5.1616161616161609</v>
+        <f t="shared" ref="G10" si="20">D10/E10</f>
+        <v>5.4789473684210526</v>
       </c>
       <c r="H10">
-        <v>38.486075999999997</v>
+        <v>38.485474000000004</v>
       </c>
       <c r="I10">
-        <v>7.2639329999999998</v>
+        <v>6.8425450000000003</v>
       </c>
       <c r="J10">
-        <v>30.910388999999999</v>
+        <v>31.405591999999999</v>
       </c>
       <c r="K10">
-        <v>5.8340839999999998</v>
+        <v>5.583774</v>
       </c>
       <c r="L10">
-        <f>J10/K10</f>
-        <v>5.2982420205125607</v>
+        <f t="shared" ref="L10" si="21">J10/K10</f>
+        <v>5.6244382383670972</v>
       </c>
       <c r="M10">
-        <f>ABS(J10-D10)/D10*100</f>
-        <v>0.81666340508805746</v>
+        <f t="shared" ref="M10" si="22">ABS(J10-D10)/D10*100</f>
+        <v>0.56225424271533198</v>
       </c>
       <c r="N10">
-        <f t="shared" si="6"/>
-        <v>1.7830976430976524</v>
+        <f t="shared" ref="N10" si="23">ABS(K10-E10)/E10*100</f>
+        <v>2.0390526315789503</v>
       </c>
       <c r="O10">
-        <f t="shared" si="0"/>
-        <v>2.646958910125945</v>
+        <f t="shared" ref="O10" si="24">(ABS(L10-G10)/G10)*100</f>
+        <v>2.6554529577087882</v>
       </c>
       <c r="P10">
-        <f t="shared" si="1"/>
-        <v>94.854375000000019</v>
+        <f t="shared" ref="P10" si="25">(F10/C10)*100</f>
+        <v>95.397106109324753</v>
       </c>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.25">
@@ -1059,57 +1059,57 @@
         <v>60</v>
       </c>
       <c r="B11">
-        <v>3.14</v>
+        <v>3.01</v>
       </c>
       <c r="C11">
         <f t="shared" si="4"/>
-        <v>188.4</v>
+        <v>180.6</v>
       </c>
       <c r="D11">
-        <v>31.28</v>
+        <v>31.84</v>
       </c>
       <c r="E11">
-        <v>5.73</v>
+        <v>5.42</v>
       </c>
       <c r="F11">
         <f>D11*E11</f>
-        <v>179.23440000000002</v>
+        <v>172.5728</v>
       </c>
       <c r="G11">
         <f t="shared" si="11"/>
-        <v>5.4589877835951128</v>
+        <v>5.8745387453874542</v>
       </c>
       <c r="H11">
-        <v>38.486243999999999</v>
+        <v>38.480384999999998</v>
       </c>
       <c r="I11">
-        <v>6.8533670000000004</v>
+        <v>6.376169</v>
       </c>
       <c r="J11">
-        <v>31.497862000000001</v>
+        <v>31.972301000000002</v>
       </c>
       <c r="K11">
-        <v>5.6089229999999999</v>
+        <v>5.2977850000000002</v>
       </c>
       <c r="L11">
         <f t="shared" si="7"/>
-        <v>5.6156702454285794</v>
+        <v>6.0350318104641847</v>
       </c>
       <c r="M11">
         <f t="shared" si="5"/>
-        <v>0.69648976982097255</v>
+        <v>0.41551821608040762</v>
       </c>
       <c r="N11">
         <f t="shared" si="6"/>
-        <v>2.1130366492146688</v>
+        <v>2.2548892988929841</v>
       </c>
       <c r="O11">
         <f t="shared" si="0"/>
-        <v>2.8701742528956635</v>
+        <v>2.7320113464694691</v>
       </c>
       <c r="P11">
         <f t="shared" si="1"/>
-        <v>95.13503184713376</v>
+        <v>95.555260243632347</v>
       </c>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.25">
@@ -1117,57 +1117,57 @@
         <v>60</v>
       </c>
       <c r="B12">
-        <v>3.03</v>
+        <v>2.91</v>
       </c>
       <c r="C12">
         <f t="shared" si="4"/>
-        <v>181.79999999999998</v>
+        <v>174.60000000000002</v>
       </c>
       <c r="D12">
-        <v>31.89</v>
+        <v>32.32</v>
       </c>
       <c r="E12">
-        <v>5.43</v>
+        <v>5.16</v>
       </c>
       <c r="F12">
         <f>D12*E12</f>
-        <v>173.1627</v>
+        <v>166.77119999999999</v>
       </c>
       <c r="G12">
         <f t="shared" si="11"/>
-        <v>5.8729281767955808</v>
+        <v>6.2635658914728678</v>
       </c>
       <c r="H12">
-        <v>38.480269999999997</v>
+        <v>38.480625000000003</v>
       </c>
       <c r="I12">
-        <v>6.3953139999999999</v>
+        <v>6.0134030000000003</v>
       </c>
       <c r="J12">
-        <v>32.049357999999998</v>
+        <v>32.411503000000003</v>
       </c>
       <c r="K12">
-        <v>5.3265140000000004</v>
+        <v>5.0649759999999997</v>
       </c>
       <c r="L12">
         <f t="shared" si="7"/>
-        <v>6.0169480451942858</v>
+        <v>6.3991424638537291</v>
       </c>
       <c r="M12">
         <f t="shared" si="5"/>
-        <v>0.49971150830980698</v>
+        <v>0.28311571782179146</v>
       </c>
       <c r="N12">
         <f t="shared" si="6"/>
-        <v>1.9058195211786244</v>
+        <v>1.8415503875969079</v>
       </c>
       <c r="O12">
         <f t="shared" si="0"/>
-        <v>2.4522668090466238</v>
+        <v>2.1645269600409787</v>
       </c>
       <c r="P12">
         <f t="shared" si="1"/>
-        <v>95.249009900990117</v>
+        <v>95.516151202749128</v>
       </c>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.25">
@@ -1175,57 +1175,57 @@
         <v>60</v>
       </c>
       <c r="B13">
-        <v>2.96</v>
+        <v>2.74</v>
       </c>
       <c r="C13">
         <f t="shared" si="4"/>
-        <v>177.6</v>
+        <v>164.4</v>
       </c>
       <c r="D13">
-        <v>32.24</v>
+        <v>32.86</v>
       </c>
       <c r="E13">
-        <v>5.25</v>
+        <v>4.7699999999999996</v>
       </c>
       <c r="F13">
-        <f t="shared" ref="F13:F14" si="19">D13*E13</f>
-        <v>169.26000000000002</v>
+        <f t="shared" ref="F13:F14" si="26">D13*E13</f>
+        <v>156.7422</v>
       </c>
       <c r="G13">
         <f>D13/E13</f>
-        <v>6.1409523809523812</v>
+        <v>6.8888888888888893</v>
       </c>
       <c r="H13">
-        <v>38.480522000000001</v>
+        <v>38.485366999999997</v>
       </c>
       <c r="I13">
-        <v>6.1307859999999996</v>
+        <v>5.482672</v>
       </c>
       <c r="J13">
-        <v>32.373322000000002</v>
+        <v>32.913673000000003</v>
       </c>
       <c r="K13">
-        <v>5.1577760000000001</v>
+        <v>4.6889219999999998</v>
       </c>
       <c r="L13">
         <f t="shared" si="7"/>
-        <v>6.276604877761268</v>
+        <v>7.0194541517218676</v>
       </c>
       <c r="M13">
         <f t="shared" si="5"/>
-        <v>0.41352977667493712</v>
+        <v>0.16333840535606639</v>
       </c>
       <c r="N13">
         <f t="shared" si="6"/>
-        <v>1.7566476190476163</v>
+        <v>1.6997484276729511</v>
       </c>
       <c r="O13">
         <f t="shared" si="0"/>
-        <v>2.2089814151571208</v>
+        <v>1.8953022024142012</v>
       </c>
       <c r="P13">
         <f t="shared" si="1"/>
-        <v>95.304054054054063</v>
+        <v>95.341970802919704</v>
       </c>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.25">
@@ -1233,57 +1233,57 @@
         <v>60</v>
       </c>
       <c r="B14">
-        <v>2.87</v>
+        <v>2.63</v>
       </c>
       <c r="C14">
         <f t="shared" si="4"/>
-        <v>172.20000000000002</v>
+        <v>157.79999999999998</v>
       </c>
       <c r="D14">
-        <v>32.54</v>
+        <v>33.159999999999997</v>
       </c>
       <c r="E14">
-        <v>5.04</v>
+        <v>4.5199999999999996</v>
       </c>
       <c r="F14">
-        <f t="shared" si="19"/>
-        <v>164.0016</v>
+        <f t="shared" si="26"/>
+        <v>149.88319999999996</v>
       </c>
       <c r="G14">
         <f>D14/E14</f>
-        <v>6.4563492063492065</v>
+        <v>7.336283185840708</v>
       </c>
       <c r="H14">
-        <v>38.482475000000001</v>
+        <v>38.481772999999997</v>
       </c>
       <c r="I14">
-        <v>5.8488429999999996</v>
+        <v>5.186515</v>
       </c>
       <c r="J14">
-        <v>32.652031000000001</v>
+        <v>33.195103000000003</v>
       </c>
       <c r="K14">
-        <v>4.9626900000000003</v>
+        <v>4.473986</v>
       </c>
       <c r="L14">
         <f t="shared" si="7"/>
-        <v>6.5795024472614649</v>
+        <v>7.4195813308311651</v>
       </c>
       <c r="M14">
         <f t="shared" si="5"/>
-        <v>0.34428703134604111</v>
+        <v>0.10585946924006799</v>
       </c>
       <c r="N14">
         <f t="shared" si="6"/>
-        <v>1.5339285714285669</v>
+        <v>1.0180088495575124</v>
       </c>
       <c r="O14">
         <f t="shared" si="0"/>
-        <v>1.9074749053404501</v>
+        <v>1.1354270668180517</v>
       </c>
       <c r="P14">
         <f t="shared" si="1"/>
-        <v>95.239024390243884</v>
+        <v>94.983016476552578</v>
       </c>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.25">
@@ -1291,57 +1291,57 @@
         <v>60</v>
       </c>
       <c r="B15">
-        <v>2.74</v>
+        <v>2.4500000000000002</v>
       </c>
       <c r="C15">
         <f t="shared" si="4"/>
-        <v>164.4</v>
+        <v>147</v>
       </c>
       <c r="D15">
-        <v>33.01</v>
+        <v>33.67</v>
       </c>
       <c r="E15">
-        <v>4.72</v>
+        <v>4.1500000000000004</v>
       </c>
       <c r="F15">
-        <f t="shared" ref="F15" si="20">D15*E15</f>
-        <v>155.80719999999999</v>
+        <f t="shared" ref="F15" si="27">D15*E15</f>
+        <v>139.73050000000001</v>
       </c>
       <c r="G15">
         <f>D15/E15</f>
-        <v>6.9936440677966099</v>
+        <v>8.113253012048192</v>
       </c>
       <c r="H15">
-        <v>38.482391</v>
+        <v>38.482933000000003</v>
       </c>
       <c r="I15">
-        <v>5.4357879999999996</v>
+        <v>4.7125979999999998</v>
       </c>
       <c r="J15">
-        <v>33.04081</v>
+        <v>33.651192000000002</v>
       </c>
       <c r="K15">
-        <v>4.6671430000000003</v>
+        <v>4.1209059999999997</v>
       </c>
       <c r="L15">
         <f t="shared" si="7"/>
-        <v>7.0794509617554038</v>
+        <v>8.1659693281040635</v>
       </c>
       <c r="M15">
         <f t="shared" si="5"/>
-        <v>9.3335352923363965E-2</v>
+        <v>5.5859815859815663E-2</v>
       </c>
       <c r="N15">
         <f t="shared" si="6"/>
-        <v>1.1198516949152435</v>
+        <v>0.70106024096387021</v>
       </c>
       <c r="O15">
         <f t="shared" si="0"/>
-        <v>1.226926808498962</v>
+        <v>0.64975560330224702</v>
       </c>
       <c r="P15">
         <f t="shared" si="1"/>
-        <v>94.773236009732358</v>
+        <v>95.054761904761904</v>
       </c>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.25">
@@ -1349,57 +1349,57 @@
         <v>60</v>
       </c>
       <c r="B16">
-        <v>2.5499999999999998</v>
+        <v>1.88</v>
       </c>
       <c r="C16">
         <f t="shared" si="4"/>
-        <v>153</v>
+        <v>112.8</v>
       </c>
       <c r="D16">
-        <v>33.56</v>
+        <v>34.39</v>
       </c>
       <c r="E16">
-        <v>4.34</v>
+        <v>3.11</v>
       </c>
       <c r="F16">
         <f>D16*E16</f>
-        <v>145.65040000000002</v>
+        <v>106.9529</v>
       </c>
       <c r="G16">
-        <f t="shared" ref="G16:G19" si="21">D16/E16</f>
-        <v>7.7327188940092171</v>
+        <f t="shared" ref="G16:G19" si="28">D16/E16</f>
+        <v>11.057877813504824</v>
       </c>
       <c r="H16">
-        <v>38.482742000000002</v>
+        <v>38.483787999999997</v>
       </c>
       <c r="I16">
-        <v>4.8881009999999998</v>
+        <v>3.500327</v>
       </c>
       <c r="J16">
-        <v>33.570869000000002</v>
+        <v>34.301085999999998</v>
       </c>
       <c r="K16">
-        <v>4.2641920000000004</v>
+        <v>3.119885</v>
       </c>
       <c r="L16">
-        <f t="shared" ref="L16:L19" si="22">J16/K16</f>
-        <v>7.8727386102689554</v>
+        <f t="shared" ref="L16:L19" si="29">J16/K16</f>
+        <v>10.994343060721789</v>
       </c>
       <c r="M16">
         <f t="shared" si="5"/>
-        <v>3.2386769964241877E-2</v>
+        <v>0.25854608897936204</v>
       </c>
       <c r="N16">
         <f t="shared" si="6"/>
-        <v>1.7467281105990651</v>
+        <v>0.31784565916399177</v>
       </c>
       <c r="O16">
         <f t="shared" si="0"/>
-        <v>1.8107436488893451</v>
+        <v>0.57456551658981725</v>
       </c>
       <c r="P16">
         <f t="shared" si="1"/>
-        <v>95.196339869281061</v>
+        <v>94.816400709219863</v>
       </c>
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.25">
@@ -1407,57 +1407,57 @@
         <v>60</v>
       </c>
       <c r="B17">
-        <v>1.98</v>
+        <v>0.94</v>
       </c>
       <c r="C17">
-        <f t="shared" ref="C17:C19" si="23">A15*B17</f>
-        <v>118.8</v>
+        <f t="shared" ref="C17:C19" si="30">A15*B17</f>
+        <v>56.4</v>
       </c>
       <c r="D17">
-        <v>34.44</v>
+        <v>35.56</v>
       </c>
       <c r="E17">
-        <v>3.24</v>
+        <v>1.45</v>
       </c>
       <c r="F17">
-        <f t="shared" ref="F17:F19" si="24">D17*E17</f>
-        <v>111.5856</v>
+        <f t="shared" ref="F17:F19" si="31">D17*E17</f>
+        <v>51.562000000000005</v>
       </c>
       <c r="G17">
-        <f t="shared" si="21"/>
-        <v>10.629629629629628</v>
+        <f t="shared" si="28"/>
+        <v>24.524137931034485</v>
       </c>
       <c r="H17">
-        <v>38.969883000000003</v>
+        <v>38.970073999999997</v>
       </c>
       <c r="I17">
-        <v>3.5966900000000002</v>
+        <v>1.6906330000000001</v>
       </c>
       <c r="J17">
-        <v>34.342472000000001</v>
+        <v>35.331485999999998</v>
       </c>
       <c r="K17">
-        <v>3.1696070000000001</v>
+        <v>1.5327809999999999</v>
       </c>
       <c r="L17">
-        <f t="shared" si="22"/>
-        <v>10.834930639666053</v>
+        <f t="shared" si="29"/>
+        <v>23.050576696866674</v>
       </c>
       <c r="M17">
         <f t="shared" si="5"/>
-        <v>0.28318234610916654</v>
+        <v>0.64261529808775053</v>
       </c>
       <c r="N17">
         <f t="shared" si="6"/>
-        <v>2.1726234567901277</v>
+        <v>5.7090344827586206</v>
       </c>
       <c r="O17">
         <f t="shared" si="0"/>
-        <v>1.9314032303078352</v>
+        <v>6.0086158311117135</v>
       </c>
       <c r="P17">
         <f t="shared" si="1"/>
-        <v>93.927272727272722</v>
+        <v>91.421985815602852</v>
       </c>
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.25">
@@ -1465,115 +1465,57 @@
         <v>60</v>
       </c>
       <c r="B18">
-        <v>1.26</v>
+        <v>0.16</v>
       </c>
       <c r="C18">
-        <f t="shared" si="23"/>
-        <v>75.599999999999994</v>
+        <f t="shared" si="30"/>
+        <v>9.6</v>
       </c>
       <c r="D18">
-        <v>35.340000000000003</v>
+        <v>36.53</v>
       </c>
       <c r="E18">
-        <v>1.97</v>
+        <v>0.08</v>
       </c>
       <c r="F18">
-        <f t="shared" si="24"/>
-        <v>69.619800000000012</v>
+        <f t="shared" si="31"/>
+        <v>2.9224000000000001</v>
       </c>
       <c r="G18">
-        <f t="shared" si="21"/>
-        <v>17.939086294416246</v>
+        <f t="shared" si="28"/>
+        <v>456.625</v>
       </c>
       <c r="H18">
-        <v>38.486595000000001</v>
+        <v>38.513306</v>
       </c>
       <c r="I18">
-        <v>2.1878790000000001</v>
+        <v>0.255853</v>
       </c>
       <c r="J18">
-        <v>35.130130999999999</v>
+        <v>36.170616000000003</v>
       </c>
       <c r="K18">
-        <v>1.997071</v>
+        <v>0.24029</v>
       </c>
       <c r="L18">
-        <f t="shared" si="22"/>
-        <v>17.590827266531836</v>
+        <f t="shared" si="29"/>
+        <v>150.52901077864249</v>
       </c>
       <c r="M18">
         <f t="shared" si="5"/>
-        <v>0.59385681946803826</v>
+        <v>0.98380509170544372</v>
       </c>
       <c r="N18">
         <f t="shared" si="6"/>
-        <v>1.3741624365482268</v>
+        <v>200.36250000000001</v>
       </c>
       <c r="O18">
         <f t="shared" si="0"/>
-        <v>1.9413420626267335</v>
+        <v>67.03443508817027</v>
       </c>
       <c r="P18">
         <f t="shared" si="1"/>
-        <v>92.089682539682556</v>
-      </c>
-    </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A19">
-        <v>60</v>
-      </c>
-      <c r="B19">
-        <v>0.16</v>
-      </c>
-      <c r="C19">
-        <f t="shared" si="23"/>
-        <v>9.6</v>
-      </c>
-      <c r="D19">
-        <v>36.700000000000003</v>
-      </c>
-      <c r="E19">
-        <v>0.08</v>
-      </c>
-      <c r="F19">
-        <f t="shared" si="24"/>
-        <v>2.9360000000000004</v>
-      </c>
-      <c r="G19">
-        <f t="shared" si="21"/>
-        <v>458.75</v>
-      </c>
-      <c r="H19">
-        <v>38.511208000000003</v>
-      </c>
-      <c r="I19">
-        <v>0.26121299999999997</v>
-      </c>
-      <c r="J19">
-        <v>36.306252000000001</v>
-      </c>
-      <c r="K19">
-        <v>0.246257</v>
-      </c>
-      <c r="L19">
-        <f t="shared" si="22"/>
-        <v>147.43236537438528</v>
-      </c>
-      <c r="M19">
-        <f t="shared" si="5"/>
-        <v>1.0728828337874718</v>
-      </c>
-      <c r="N19">
-        <f t="shared" si="6"/>
-        <v>207.82124999999999</v>
-      </c>
-      <c r="O19">
-        <f t="shared" si="0"/>
-        <v>67.862154686782489</v>
-      </c>
-      <c r="P19">
-        <f t="shared" si="1"/>
-        <v>30.583333333333339</v>
+        <v>30.441666666666666</v>
       </c>
     </row>
   </sheetData>
